--- a/data/distance-maps/iilabs3d/distance-maps_iilabs3d_results.xlsx
+++ b/data/distance-maps/iilabs3d/distance-maps_iilabs3d_results.xlsx
@@ -3,26 +3,27 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30117"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C8934D1-68D4-469B-AE13-B81F7334D047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35974A7C-3FE4-4926-917A-69F70478C481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="rmax-10.0m_m0" sheetId="2" r:id="rId2"/>
-    <sheet name="rmax-10.0m_m0-1-2" sheetId="3" r:id="rId3"/>
-    <sheet name="rmax-20.0m_m0" sheetId="4" r:id="rId4"/>
-    <sheet name="rmax-20.0m_m0-1-2" sheetId="5" r:id="rId5"/>
-    <sheet name="rmax-30.0m_m0" sheetId="6" r:id="rId6"/>
-    <sheet name="rmax-30.0m_m0-1-2" sheetId="7" r:id="rId7"/>
+    <sheet name="best-best-analysis" sheetId="8" r:id="rId1"/>
+    <sheet name="best-analysis" sheetId="1" r:id="rId2"/>
+    <sheet name="rmax-10.0m_m0" sheetId="2" r:id="rId3"/>
+    <sheet name="rmax-10.0m_m0-1-2" sheetId="3" r:id="rId4"/>
+    <sheet name="rmax-20.0m_m0" sheetId="4" r:id="rId5"/>
+    <sheet name="rmax-20.0m_m0-1-2" sheetId="5" r:id="rId6"/>
+    <sheet name="rmax-30.0m_m0" sheetId="6" r:id="rId7"/>
+    <sheet name="rmax-30.0m_m0-1-2" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="1" hidden="1">'rmax-10.0m_m0'!$A$1:$K$49</definedName>
-    <definedName name="ExternalData_1" localSheetId="2" hidden="1">'rmax-10.0m_m0-1-2'!$A$1:$K$49</definedName>
-    <definedName name="ExternalData_1" localSheetId="3" hidden="1">'rmax-20.0m_m0'!$A$1:$K$49</definedName>
-    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'rmax-20.0m_m0-1-2'!$A$1:$K$49</definedName>
-    <definedName name="ExternalData_1" localSheetId="5" hidden="1">'rmax-30.0m_m0'!$A$1:$K$49</definedName>
-    <definedName name="ExternalData_1" localSheetId="6" hidden="1">'rmax-30.0m_m0-1-2'!$A$1:$K$49</definedName>
+    <definedName name="ExternalData_1" localSheetId="2" hidden="1">'rmax-10.0m_m0'!$A$1:$K$49</definedName>
+    <definedName name="ExternalData_1" localSheetId="3" hidden="1">'rmax-10.0m_m0-1-2'!$A$1:$K$49</definedName>
+    <definedName name="ExternalData_1" localSheetId="4" hidden="1">'rmax-20.0m_m0'!$A$1:$K$49</definedName>
+    <definedName name="ExternalData_1" localSheetId="5" hidden="1">'rmax-20.0m_m0-1-2'!$A$1:$K$49</definedName>
+    <definedName name="ExternalData_1" localSheetId="6" hidden="1">'rmax-30.0m_m0'!$A$1:$K$49</definedName>
+    <definedName name="ExternalData_1" localSheetId="7" hidden="1">'rmax-30.0m_m0-1-2'!$A$1:$K$49</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -68,7 +69,109 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="62">
+  <si>
+    <t>10.0m</t>
+  </si>
+  <si>
+    <t>20.0m</t>
+  </si>
+  <si>
+    <t>30.0m</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>RTE</t>
+  </si>
+  <si>
+    <t>RRE</t>
+  </si>
+  <si>
+    <t>Nav A Diff</t>
+  </si>
+  <si>
+    <t>icp_p2pl_inliers-60%</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_inliers-40%</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_inliers-50% / dmap_p2pl_m2_inliers-40%</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_inliers-40/50%</t>
+  </si>
+  <si>
+    <t>icp_p2pl_inliers-40%</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_inliers-50%</t>
+  </si>
+  <si>
+    <t>Nav A Omni</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_trans-0.50m</t>
+  </si>
+  <si>
+    <t>icp_p2pl_inliers-70%</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_trans-1.00m</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_inliers-70%</t>
+  </si>
+  <si>
+    <t>Loop</t>
+  </si>
+  <si>
+    <t>dmap_p2pl_m0_inliers-90%</t>
+  </si>
+  <si>
+    <t>dmap_p2pl_m0/m2_inliers-40%</t>
+  </si>
+  <si>
+    <t>Slippage</t>
+  </si>
+  <si>
+    <t>icp_p2p_trans-2.00m</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m0_trans-3.00m</t>
+  </si>
+  <si>
+    <t>icp_p2p_trans-2.50/inliers-60%</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m0_trans-2.50m</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m1_trans-2.00m</t>
+  </si>
+  <si>
+    <t>icp_p2p_trans-3.00m</t>
+  </si>
+  <si>
+    <t>Best variant across all configurations</t>
+  </si>
+  <si>
+    <t>10.0m -&gt; 20.0m</t>
+  </si>
+  <si>
+    <t>20.0m-&gt;30.0m</t>
+  </si>
+  <si>
+    <t>icp_p2p_trans-2.50m</t>
+  </si>
+  <si>
+    <t>Best dmap_p2p_m1 vs icp and dmap m0 across all configurations</t>
+  </si>
+  <si>
+    <t>dmap_p2p_m0_inliers-50%</t>
+  </si>
   <si>
     <t>Column1</t>
   </si>
@@ -158,7 +261,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +285,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -213,12 +324,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -828,15 +952,789 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{726BBEFC-4F9E-4A7F-A3F8-E58C8A23A07E}">
+  <dimension ref="A3:P8"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.7109375" customWidth="1"/>
+    <col min="8" max="8" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="25.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:16">
+      <c r="C3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="H3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="M3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" t="s">
+        <v>4</v>
+      </c>
+      <c r="J4" t="s">
+        <v>3</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O4" t="s">
+        <v>3</v>
+      </c>
+      <c r="P4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>1.02</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="H5" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5">
+        <v>0.98</v>
+      </c>
+      <c r="J5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="7">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>0.88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6">
+        <v>7.5999999999999998E-2</v>
+      </c>
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6">
+        <v>0.83</v>
+      </c>
+      <c r="J6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="7">
+        <v>6.3E-2</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" s="7">
+        <v>6.3E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>1.79</v>
+      </c>
+      <c r="E7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7">
+        <v>0.13800000000000001</v>
+      </c>
+      <c r="H7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7">
+        <v>1.74</v>
+      </c>
+      <c r="J7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7">
+        <v>0.121</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="P7" s="7">
+        <v>0.106</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7">
+        <v>3.3000000000000002E-2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8">
+        <v>0.47</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="M8" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O8" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8">
+        <v>3.7999999999999999E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="M3:P3"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:T17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="2.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="52.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.7109375" customWidth="1"/>
+    <col min="11" max="11" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="A1" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="K3" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="P3" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q3" s="8"/>
+      <c r="S3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" s="8"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" t="s">
+        <v>4</v>
+      </c>
+      <c r="M4" t="s">
+        <v>5</v>
+      </c>
+      <c r="P4" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>5</v>
+      </c>
+      <c r="S4" t="s">
+        <v>4</v>
+      </c>
+      <c r="T4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="A5" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5">
+        <v>1.02</v>
+      </c>
+      <c r="E5">
+        <v>0.105</v>
+      </c>
+      <c r="G5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5">
+        <v>0.98</v>
+      </c>
+      <c r="I5">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="7">
+        <v>0.88</v>
+      </c>
+      <c r="M5" s="7">
+        <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="P5" s="6">
+        <f>(H5-D5)/D5</f>
+        <v>-3.9215686274509838E-2</v>
+      </c>
+      <c r="Q5" s="6">
+        <f t="shared" ref="Q5:Q8" si="0">(I5-E5)/E5</f>
+        <v>-0.19047619047619038</v>
+      </c>
+      <c r="S5" s="6">
+        <f>(L5-H5)/H5</f>
+        <v>-0.10204081632653059</v>
+      </c>
+      <c r="T5" s="6">
+        <f t="shared" ref="T5:T8" si="1">(M5-I5)/I5</f>
+        <v>-3.5294117647058851E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6">
+        <v>0.88</v>
+      </c>
+      <c r="E6">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6">
+        <v>0.83</v>
+      </c>
+      <c r="I6">
+        <v>0.08</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="M6" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" ref="P6:P8" si="2">(H6-D6)/D6</f>
+        <v>-5.6818181818181872E-2</v>
+      </c>
+      <c r="Q6" s="6">
+        <f t="shared" si="0"/>
+        <v>-6.9767441860465018E-2</v>
+      </c>
+      <c r="S6" s="6">
+        <f t="shared" ref="S6:S8" si="3">(L6-H6)/H6</f>
+        <v>-2.4096385542168565E-2</v>
+      </c>
+      <c r="T6" s="6">
+        <f t="shared" si="1"/>
+        <v>-0.1875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="A7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>1.79</v>
+      </c>
+      <c r="E7">
+        <v>0.153</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7">
+        <v>1.74</v>
+      </c>
+      <c r="I7">
+        <v>0.123</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="7">
+        <v>1.37</v>
+      </c>
+      <c r="M7" s="7">
+        <v>0.106</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="2"/>
+        <v>-2.7932960893854771E-2</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="0"/>
+        <v>-0.19607843137254902</v>
+      </c>
+      <c r="S7" s="6">
+        <f t="shared" si="3"/>
+        <v>-0.21264367816091947</v>
+      </c>
+      <c r="T7" s="6">
+        <f t="shared" si="1"/>
+        <v>-0.13821138211382114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
+        <v>0.47</v>
+      </c>
+      <c r="I8">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="K8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="L8" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M8" s="7">
+        <v>5.6000000000000001E-2</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="2"/>
+        <v>4.4444444444444363E-2</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555608E-2</v>
+      </c>
+      <c r="S8" s="6">
+        <f t="shared" si="3"/>
+        <v>0.17021276595744697</v>
+      </c>
+      <c r="T8" s="6">
+        <f t="shared" si="1"/>
+        <v>-1.7543859649122823E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="A10" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="C12" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="G12" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="K12" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="C13" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>3</v>
+      </c>
+      <c r="H13" t="s">
+        <v>4</v>
+      </c>
+      <c r="I13" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" t="s">
+        <v>3</v>
+      </c>
+      <c r="L13" t="s">
+        <v>4</v>
+      </c>
+      <c r="M13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="A14" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E14">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14">
+        <v>0.98</v>
+      </c>
+      <c r="I14">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L14" s="7">
+        <v>0.95</v>
+      </c>
+      <c r="M14" s="7">
+        <v>7.8E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="A15" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15">
+        <v>0.88</v>
+      </c>
+      <c r="E15">
+        <v>8.5999999999999993E-2</v>
+      </c>
+      <c r="G15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15">
+        <v>0.84</v>
+      </c>
+      <c r="I15">
+        <v>6.7000000000000004E-2</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="L15" s="7">
+        <v>0.81</v>
+      </c>
+      <c r="M15" s="7">
+        <v>6.5000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="A16" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16">
+        <v>2.56</v>
+      </c>
+      <c r="E16">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="G16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H16">
+        <v>2.29</v>
+      </c>
+      <c r="I16">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L16" s="7">
+        <v>2.14</v>
+      </c>
+      <c r="M16" s="7">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="E17" s="7">
+        <v>5.3999999999999999E-2</v>
+      </c>
+      <c r="G17" t="s">
+        <v>31</v>
+      </c>
+      <c r="H17">
+        <v>0.47</v>
+      </c>
+      <c r="I17">
+        <v>5.7000000000000002E-2</v>
+      </c>
+      <c r="K17" t="s">
+        <v>26</v>
+      </c>
+      <c r="L17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="M17">
+        <v>5.6000000000000001E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="K12:M12"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC5BFC7-661B-44F1-B575-D69CB53AAAA7}">
   <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -854,45 +1752,45 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2">
         <v>3.13</v>
@@ -918,16 +1816,16 @@
       <c r="J2">
         <v>0.105</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
+      <c r="K2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3">
         <v>2.2000000000000002</v>
@@ -953,16 +1851,16 @@
       <c r="J3">
         <v>0.08</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1.79</v>
@@ -988,16 +1886,16 @@
       <c r="J4">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
+      <c r="K4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1.56</v>
@@ -1017,22 +1915,22 @@
       <c r="H5">
         <v>0.17899999999999999</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>0.7</v>
       </c>
       <c r="J5">
         <v>6.2E-2</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>13</v>
+      <c r="K5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
       </c>
       <c r="C6">
         <v>1.41</v>
@@ -1058,16 +1956,16 @@
       <c r="J6">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
+      <c r="K6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1.66</v>
@@ -1075,10 +1973,10 @@
       <c r="D7">
         <v>0.14299999999999999</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="3">
         <v>1.23</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="G7">
@@ -1090,24 +1988,24 @@
       <c r="I7">
         <v>0.82</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
+      <c r="K7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.36</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>0.115</v>
       </c>
       <c r="E8">
@@ -1116,10 +2014,10 @@
       <c r="F8">
         <v>0.106</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>2.56</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <v>0.16700000000000001</v>
       </c>
       <c r="I8">
@@ -1128,16 +2026,16 @@
       <c r="J8">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>13</v>
+      <c r="K8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
       </c>
       <c r="C9">
         <v>1.41</v>
@@ -1163,16 +2061,16 @@
       <c r="J9">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>13</v>
+      <c r="K9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.61</v>
@@ -1198,16 +2096,16 @@
       <c r="J10">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>13</v>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
       </c>
       <c r="C11">
         <v>1.95</v>
@@ -1233,16 +2131,16 @@
       <c r="J11">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12">
         <v>2.5</v>
@@ -1268,51 +2166,51 @@
       <c r="J12">
         <v>0.104</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>13</v>
+      <c r="K12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1">
         <v>5.25</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>0.221</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>4.12</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>0.159</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>10.62</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>0.39</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>2.61</v>
       </c>
       <c r="J13">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>13</v>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14">
         <v>1.55</v>
@@ -1338,16 +2236,16 @@
       <c r="J14">
         <v>0.13200000000000001</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>13</v>
+      <c r="K14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>1.45</v>
@@ -1373,16 +2271,16 @@
       <c r="J15">
         <v>0.1</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>13</v>
+      <c r="K15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1.37</v>
@@ -1408,16 +2306,16 @@
       <c r="J16">
         <v>0.115</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>13</v>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
       </c>
       <c r="C17">
         <v>1.2</v>
@@ -1443,16 +2341,16 @@
       <c r="J17">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>13</v>
+      <c r="K17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18">
         <v>1.1599999999999999</v>
@@ -1460,7 +2358,7 @@
       <c r="D18">
         <v>0.113</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <v>0.97</v>
       </c>
       <c r="F18">
@@ -1472,22 +2370,22 @@
       <c r="H18">
         <v>0.20599999999999999</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="3">
         <v>0.68</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="3">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>13</v>
+      <c r="K18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19">
         <v>1.72</v>
@@ -1513,21 +2411,21 @@
       <c r="J19">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>13</v>
+      <c r="K19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
       </c>
       <c r="C20">
         <v>1.1299999999999999</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>0.104</v>
       </c>
       <c r="E20">
@@ -1536,7 +2434,7 @@
       <c r="F20">
         <v>0.125</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>1.81</v>
       </c>
       <c r="H20">
@@ -1548,24 +2446,24 @@
       <c r="J20">
         <v>0.11899999999999999</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>13</v>
+      <c r="K20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
       </c>
       <c r="C21">
         <v>1.0900000000000001</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="3">
         <v>0.104</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>0.97</v>
       </c>
       <c r="F21">
@@ -1583,18 +2481,18 @@
       <c r="J21">
         <v>0.107</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>13</v>
+      <c r="K21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" s="4">
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="3">
         <v>1.03</v>
       </c>
       <c r="D22">
@@ -1603,7 +2501,7 @@
       <c r="E22">
         <v>1.03</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="G22">
@@ -1618,16 +2516,16 @@
       <c r="J22">
         <v>0.11799999999999999</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>13</v>
+      <c r="K22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23">
         <v>1.18</v>
@@ -1653,16 +2551,16 @@
       <c r="J23">
         <v>7.8E-2</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>13</v>
+      <c r="K23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
       </c>
       <c r="C24">
         <v>1.87</v>
@@ -1688,51 +2586,51 @@
       <c r="J24">
         <v>7.8E-2</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>13</v>
+      <c r="K24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1">
         <v>8.4499999999999993</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>0.23300000000000001</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>9.23</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>0.23</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="1">
         <v>8.32</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="3">
         <v>0.13800000000000001</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="1">
         <v>7.12</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>0.16700000000000001</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
+      <c r="K25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
       </c>
       <c r="C26">
         <v>3.14</v>
@@ -1758,16 +2656,16 @@
       <c r="J26">
         <v>0.104</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
+      <c r="K26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
         <v>2.2000000000000002</v>
@@ -1793,16 +2691,16 @@
       <c r="J27">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
+      <c r="K27" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1.69</v>
@@ -1828,16 +2726,16 @@
       <c r="J28">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>13</v>
+      <c r="K28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>16</v>
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1.62</v>
@@ -1863,16 +2761,16 @@
       <c r="J29">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
+      <c r="K29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1.34</v>
@@ -1898,16 +2796,16 @@
       <c r="J30">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>13</v>
+      <c r="K30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1.57</v>
@@ -1933,16 +2831,16 @@
       <c r="J31">
         <v>3.9E-2</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>13</v>
+      <c r="K31" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1.34</v>
@@ -1968,16 +2866,16 @@
       <c r="J32">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
+      <c r="K32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1.45</v>
@@ -2003,16 +2901,16 @@
       <c r="J33">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
+      <c r="K33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1.56</v>
@@ -2038,16 +2936,16 @@
       <c r="J34">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
+      <c r="K34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1.85</v>
@@ -2073,16 +2971,16 @@
       <c r="J35">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
+      <c r="K35" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>23</v>
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
       </c>
       <c r="C36">
         <v>2.4500000000000002</v>
@@ -2108,51 +3006,51 @@
       <c r="J36">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
+      <c r="K36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="1">
         <v>5</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>0.216</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>4.07</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>0.16300000000000001</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="1">
         <v>10.93</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>0.40699999999999997</v>
       </c>
-      <c r="I37" s="3">
+      <c r="I37" s="2">
         <v>2.61</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="1">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
+      <c r="K37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1.55</v>
@@ -2178,16 +3076,16 @@
       <c r="J38">
         <v>0.13400000000000001</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
+      <c r="K38" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
       </c>
       <c r="C39">
         <v>1.45</v>
@@ -2213,16 +3111,16 @@
       <c r="J39">
         <v>0.1</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
+      <c r="K39" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
       <c r="C40">
         <v>1.38</v>
@@ -2248,16 +3146,16 @@
       <c r="J40">
         <v>0.115</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
+      <c r="K40" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1.23</v>
@@ -2283,16 +3181,16 @@
       <c r="J41">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>13</v>
+      <c r="K41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
       </c>
       <c r="C42">
         <v>1.1499999999999999</v>
@@ -2318,16 +3216,16 @@
       <c r="J42">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
+      <c r="K42" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1.78</v>
@@ -2353,16 +3251,16 @@
       <c r="J43">
         <v>6.3E-2</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>13</v>
+      <c r="K43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
       </c>
       <c r="C44">
         <v>1.17</v>
@@ -2388,16 +3286,16 @@
       <c r="J44">
         <v>0.11899999999999999</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
+      <c r="K44" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1.1299999999999999</v>
@@ -2423,16 +3321,16 @@
       <c r="J45">
         <v>0.107</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>13</v>
+      <c r="K45" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>21</v>
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1.02</v>
@@ -2458,16 +3356,16 @@
       <c r="J46">
         <v>0.108</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>13</v>
+      <c r="K46" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1.19</v>
@@ -2493,16 +3391,16 @@
       <c r="J47">
         <v>0.08</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
+      <c r="K47" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
       </c>
       <c r="C48">
         <v>1.88</v>
@@ -2528,43 +3426,43 @@
       <c r="J48">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
+      <c r="K48" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1">
         <v>8.44</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>0.23100000000000001</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>9.18</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>0.23699999999999999</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="1">
         <v>8.2799999999999994</v>
       </c>
       <c r="H49">
         <v>0.13900000000000001</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="1">
         <v>7.1</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>0.16800000000000001</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
+      <c r="K49" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -2575,7 +3473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B76EC4F-1F48-4960-B6B9-A61DD8E13A35}">
   <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2593,45 +3491,45 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2">
         <v>1.68</v>
@@ -2657,16 +3555,16 @@
       <c r="J2">
         <v>0.155</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
+      <c r="K2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3">
         <v>1.35</v>
@@ -2692,16 +3590,16 @@
       <c r="J3">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1.1599999999999999</v>
@@ -2727,16 +3625,16 @@
       <c r="J4">
         <v>0.112</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
+      <c r="K4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1.2</v>
@@ -2756,22 +3654,22 @@
       <c r="H5">
         <v>0.219</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>0.57999999999999996</v>
       </c>
       <c r="J5">
         <v>7.0999999999999994E-2</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>13</v>
+      <c r="K5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
       </c>
       <c r="C6">
         <v>1.25</v>
@@ -2797,16 +3695,16 @@
       <c r="J6">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
+      <c r="K6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1.37</v>
@@ -2817,7 +3715,7 @@
       <c r="E7">
         <v>1.33</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>0.124</v>
       </c>
       <c r="G7">
@@ -2832,21 +3730,21 @@
       <c r="J7">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
+      <c r="K7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.0900000000000001</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>0.10100000000000001</v>
       </c>
       <c r="E8">
@@ -2855,28 +3753,28 @@
       <c r="F8">
         <v>0.108</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>2.81</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <v>0.17699999999999999</v>
       </c>
       <c r="I8">
         <v>0.66</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>13</v>
+      <c r="K8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
       </c>
       <c r="C9">
         <v>1.1100000000000001</v>
@@ -2884,7 +3782,7 @@
       <c r="D9">
         <v>0.108</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>0.88</v>
       </c>
       <c r="F9">
@@ -2902,16 +3800,16 @@
       <c r="J9">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>13</v>
+      <c r="K9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.1200000000000001</v>
@@ -2937,16 +3835,16 @@
       <c r="J10">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>13</v>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
       </c>
       <c r="C11">
         <v>1.3</v>
@@ -2972,16 +3870,16 @@
       <c r="J11">
         <v>0.11</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12">
         <v>1.43</v>
@@ -3007,16 +3905,16 @@
       <c r="J12">
         <v>0.13700000000000001</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>13</v>
+      <c r="K12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
       </c>
       <c r="C13">
         <v>2.09</v>
@@ -3042,16 +3940,16 @@
       <c r="J13">
         <v>0.182</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>13</v>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14">
         <v>1.37</v>
@@ -3077,16 +3975,16 @@
       <c r="J14">
         <v>7.8E-2</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>13</v>
+      <c r="K14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>1.35</v>
@@ -3112,16 +4010,16 @@
       <c r="J15">
         <v>0.111</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>13</v>
+      <c r="K15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1.36</v>
@@ -3129,7 +4027,7 @@
       <c r="D16">
         <v>0.13600000000000001</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>1.1000000000000001</v>
       </c>
       <c r="F16">
@@ -3144,19 +4042,19 @@
       <c r="I16">
         <v>0.8</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="3">
         <v>0.05</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>13</v>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
       </c>
       <c r="C17">
         <v>1.38</v>
@@ -3182,16 +4080,16 @@
       <c r="J17">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>13</v>
+      <c r="K17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18">
         <v>1.33</v>
@@ -3217,21 +4115,21 @@
       <c r="J18">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>13</v>
+      <c r="K18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19">
         <v>1.23</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>0.11700000000000001</v>
       </c>
       <c r="E19">
@@ -3252,18 +4150,18 @@
       <c r="J19">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>13</v>
+      <c r="K19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3">
         <v>1.21</v>
       </c>
       <c r="D20">
@@ -3275,7 +4173,7 @@
       <c r="F20">
         <v>0.13200000000000001</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>2.13</v>
       </c>
       <c r="H20">
@@ -3287,16 +4185,16 @@
       <c r="J20">
         <v>0.13100000000000001</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>13</v>
+      <c r="K20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
       </c>
       <c r="C21">
         <v>1.28</v>
@@ -3313,7 +4211,7 @@
       <c r="G21">
         <v>2.6</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="3">
         <v>0.14299999999999999</v>
       </c>
       <c r="I21">
@@ -3322,16 +4220,16 @@
       <c r="J21">
         <v>0.11600000000000001</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>13</v>
+      <c r="K21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22">
         <v>1.31</v>
@@ -3342,7 +4240,7 @@
       <c r="E22">
         <v>1.1100000000000001</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="3">
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="G22">
@@ -3357,16 +4255,16 @@
       <c r="J22">
         <v>0.13200000000000001</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>13</v>
+      <c r="K22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23">
         <v>1.36</v>
@@ -3386,22 +4284,22 @@
       <c r="H23">
         <v>0.23400000000000001</v>
       </c>
-      <c r="I23" s="4">
+      <c r="I23" s="3">
         <v>0.75</v>
       </c>
       <c r="J23">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>13</v>
+      <c r="K23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
       </c>
       <c r="C24">
         <v>1.36</v>
@@ -3427,16 +4325,16 @@
       <c r="J24">
         <v>0.13300000000000001</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>13</v>
+      <c r="K24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
       </c>
       <c r="C25">
         <v>13.15</v>
@@ -3462,16 +4360,16 @@
       <c r="J25">
         <v>0.504</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
+      <c r="K25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
       </c>
       <c r="C26">
         <v>3.14</v>
@@ -3497,16 +4395,16 @@
       <c r="J26">
         <v>0.104</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
+      <c r="K26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
         <v>2.2000000000000002</v>
@@ -3532,16 +4430,16 @@
       <c r="J27">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
+      <c r="K27" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1.69</v>
@@ -3567,16 +4465,16 @@
       <c r="J28">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>13</v>
+      <c r="K28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>16</v>
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1.62</v>
@@ -3590,36 +4488,36 @@
       <c r="F29">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="3">
         <v>2.75</v>
       </c>
       <c r="H29">
         <v>0.18</v>
       </c>
-      <c r="I29" s="4">
+      <c r="I29" s="3">
         <v>0.45</v>
       </c>
       <c r="J29">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
+      <c r="K29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="4">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
+      </c>
+      <c r="C30" s="3">
         <v>1.34</v>
       </c>
-      <c r="D30" s="4">
+      <c r="D30" s="3">
         <v>0.109</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="3">
         <v>1.1599999999999999</v>
       </c>
       <c r="F30">
@@ -3637,16 +4535,16 @@
       <c r="J30">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>13</v>
+      <c r="K30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1.57</v>
@@ -3669,19 +4567,19 @@
       <c r="I31">
         <v>0.68</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="3">
         <v>3.9E-2</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>13</v>
+      <c r="K31" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1.34</v>
@@ -3698,7 +4596,7 @@
       <c r="G32">
         <v>2.89</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="3">
         <v>0.17599999999999999</v>
       </c>
       <c r="I32">
@@ -3707,16 +4605,16 @@
       <c r="J32">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
+      <c r="K32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1.45</v>
@@ -3742,16 +4640,16 @@
       <c r="J33">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
+      <c r="K33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1.56</v>
@@ -3777,16 +4675,16 @@
       <c r="J34">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
+      <c r="K34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1.85</v>
@@ -3812,16 +4710,16 @@
       <c r="J35">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
+      <c r="K35" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>23</v>
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
       </c>
       <c r="C36">
         <v>2.4500000000000002</v>
@@ -3832,7 +4730,7 @@
       <c r="E36">
         <v>2.13</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="3">
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="G36">
@@ -3847,16 +4745,16 @@
       <c r="J36">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
+      <c r="K36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>24</v>
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -3882,16 +4780,16 @@
       <c r="J37">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
+      <c r="K37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1.55</v>
@@ -3917,16 +4815,16 @@
       <c r="J38">
         <v>0.13400000000000001</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
+      <c r="K38" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
       </c>
       <c r="C39">
         <v>1.45</v>
@@ -3952,16 +4850,16 @@
       <c r="J39">
         <v>0.1</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
+      <c r="K39" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
       <c r="C40">
         <v>1.38</v>
@@ -3987,16 +4885,16 @@
       <c r="J40">
         <v>0.115</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
+      <c r="K40" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1.23</v>
@@ -4022,16 +4920,16 @@
       <c r="J41">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>13</v>
+      <c r="K41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
       </c>
       <c r="C42">
         <v>1.1499999999999999</v>
@@ -4057,16 +4955,16 @@
       <c r="J42">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
+      <c r="K42" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1.78</v>
@@ -4086,27 +4984,27 @@
       <c r="H43">
         <v>0.151</v>
       </c>
-      <c r="I43" s="4">
+      <c r="I43" s="3">
         <v>0.64</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="3">
         <v>6.3E-2</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>13</v>
+      <c r="K43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
       </c>
       <c r="C44">
         <v>1.17</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>0.10199999999999999</v>
       </c>
       <c r="E44">
@@ -4115,7 +5013,7 @@
       <c r="F44">
         <v>0.11799999999999999</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="3">
         <v>1.79</v>
       </c>
       <c r="H44">
@@ -4127,16 +5025,16 @@
       <c r="J44">
         <v>0.11899999999999999</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
+      <c r="K44" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1.1299999999999999</v>
@@ -4144,7 +5042,7 @@
       <c r="D45">
         <v>0.113</v>
       </c>
-      <c r="E45" s="4">
+      <c r="E45" s="3">
         <v>0.91</v>
       </c>
       <c r="F45">
@@ -4162,18 +5060,18 @@
       <c r="J45">
         <v>0.107</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>13</v>
+      <c r="K45" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" s="4">
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="3">
         <v>1.02</v>
       </c>
       <c r="D46">
@@ -4197,16 +5095,16 @@
       <c r="J46">
         <v>0.108</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>13</v>
+      <c r="K46" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1.19</v>
@@ -4217,7 +5115,7 @@
       <c r="E47">
         <v>0.95</v>
       </c>
-      <c r="F47" s="4">
+      <c r="F47" s="3">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="G47">
@@ -4232,16 +5130,16 @@
       <c r="J47">
         <v>0.08</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
+      <c r="K47" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
       </c>
       <c r="C48">
         <v>1.88</v>
@@ -4267,16 +5165,16 @@
       <c r="J48">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
+      <c r="K48" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>24</v>
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
       </c>
       <c r="C49">
         <v>8.44</v>
@@ -4293,7 +5191,7 @@
       <c r="G49">
         <v>8.2799999999999994</v>
       </c>
-      <c r="H49" s="4">
+      <c r="H49" s="3">
         <v>0.13900000000000001</v>
       </c>
       <c r="I49">
@@ -4302,8 +5200,8 @@
       <c r="J49">
         <v>0.16800000000000001</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
+      <c r="K49" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -4314,7 +5212,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F243C2C4-651A-45C9-8FD5-109D51DDDD91}">
   <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4332,45 +5230,45 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2">
         <v>3.01</v>
@@ -4396,16 +5294,16 @@
       <c r="J2">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
+      <c r="K2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3">
         <v>2.04</v>
@@ -4431,16 +5329,16 @@
       <c r="J3">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1.78</v>
@@ -4466,16 +5364,16 @@
       <c r="J4">
         <v>0.05</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
+      <c r="K4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1.5</v>
@@ -4495,22 +5393,22 @@
       <c r="H5">
         <v>0.19900000000000001</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>0.52</v>
       </c>
       <c r="J5">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>13</v>
+      <c r="K5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
       </c>
       <c r="C6">
         <v>1.3</v>
@@ -4533,19 +5431,19 @@
       <c r="I6">
         <v>0.53</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>3.5999999999999997E-2</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
+      <c r="K6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1.55</v>
@@ -4571,30 +5469,30 @@
       <c r="J7">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
+      <c r="K7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.17</v>
       </c>
       <c r="D8">
         <v>0.114</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>1.1599999999999999</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>2.58</v>
       </c>
       <c r="H8">
@@ -4606,21 +5504,21 @@
       <c r="J8">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>13</v>
+      <c r="K8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
       </c>
       <c r="C9">
         <v>1.38</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>0.11</v>
       </c>
       <c r="E9">
@@ -4632,7 +5530,7 @@
       <c r="G9">
         <v>2.99</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>0.14099999999999999</v>
       </c>
       <c r="I9">
@@ -4641,16 +5539,16 @@
       <c r="J9">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>13</v>
+      <c r="K9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.6</v>
@@ -4676,16 +5574,16 @@
       <c r="J10">
         <v>3.9E-2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>13</v>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
       </c>
       <c r="C11">
         <v>1.86</v>
@@ -4711,16 +5609,16 @@
       <c r="J11">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12">
         <v>2.4500000000000002</v>
@@ -4746,51 +5644,51 @@
       <c r="J12">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>13</v>
+      <c r="K12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1">
         <v>5.38</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>0.311</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>4.0199999999999996</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="1">
         <v>0.186</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>9.76</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>0.41</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>2.4700000000000002</v>
       </c>
       <c r="J13">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>13</v>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14">
         <v>1.65</v>
@@ -4816,16 +5714,16 @@
       <c r="J14">
         <v>0.12</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>13</v>
+      <c r="K14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>1.33</v>
@@ -4851,16 +5749,16 @@
       <c r="J15">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>13</v>
+      <c r="K15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1.28</v>
@@ -4886,16 +5784,16 @@
       <c r="J16">
         <v>0.115</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>13</v>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
       </c>
       <c r="C17">
         <v>1.1100000000000001</v>
@@ -4906,7 +5804,7 @@
       <c r="E17">
         <v>0.87</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G17">
@@ -4921,18 +5819,18 @@
       <c r="J17">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>13</v>
+      <c r="K17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="4">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="3">
         <v>1.05</v>
       </c>
       <c r="D18">
@@ -4956,16 +5854,16 @@
       <c r="J18">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>13</v>
+      <c r="K18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19">
         <v>1.53</v>
@@ -4988,24 +5886,24 @@
       <c r="I19">
         <v>0.71</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>13</v>
+      <c r="K19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
       </c>
       <c r="C20">
         <v>1.06</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>0.09</v>
       </c>
       <c r="E20">
@@ -5014,10 +5912,10 @@
       <c r="F20">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>1.75</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="3">
         <v>0.121</v>
       </c>
       <c r="I20">
@@ -5026,16 +5924,16 @@
       <c r="J20">
         <v>7.8E-2</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>13</v>
+      <c r="K20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
       </c>
       <c r="C21">
         <v>1.1499999999999999</v>
@@ -5055,22 +5953,22 @@
       <c r="H21">
         <v>0.14599999999999999</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="3">
         <v>0.65</v>
       </c>
       <c r="J21">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>13</v>
+      <c r="K21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22">
         <v>1.1000000000000001</v>
@@ -5078,7 +5976,7 @@
       <c r="D22">
         <v>0.104</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>0.84</v>
       </c>
       <c r="F22">
@@ -5096,16 +5994,16 @@
       <c r="J22">
         <v>0.11799999999999999</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>13</v>
+      <c r="K22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23">
         <v>1.23</v>
@@ -5122,7 +6020,7 @@
       <c r="G23">
         <v>3.66</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="1">
         <v>0.216</v>
       </c>
       <c r="I23">
@@ -5131,16 +6029,16 @@
       <c r="J23">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>13</v>
+      <c r="K23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
       </c>
       <c r="C24">
         <v>3.04</v>
@@ -5154,63 +6052,63 @@
       <c r="F24">
         <v>0.214</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="1">
         <v>6.84</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>0.255</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="1">
         <v>5.08</v>
       </c>
       <c r="J24">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>13</v>
+      <c r="K24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1">
         <v>7.97</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>0.215</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>9.5</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>0.21099999999999999</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="1">
         <v>8.2899999999999991</v>
       </c>
       <c r="H25">
         <v>0.13700000000000001</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="1">
         <v>6.99</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>0.24199999999999999</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
+      <c r="K25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
       </c>
       <c r="C26">
         <v>3.01</v>
@@ -5236,16 +6134,16 @@
       <c r="J26">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
+      <c r="K26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
         <v>2.0499999999999998</v>
@@ -5271,16 +6169,16 @@
       <c r="J27">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
+      <c r="K27" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1.69</v>
@@ -5306,16 +6204,16 @@
       <c r="J28">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>13</v>
+      <c r="K28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>16</v>
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1.42</v>
@@ -5341,16 +6239,16 @@
       <c r="J29">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
+      <c r="K29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1.31</v>
@@ -5376,16 +6274,16 @@
       <c r="J30">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>13</v>
+      <c r="K30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1.55</v>
@@ -5411,16 +6309,16 @@
       <c r="J31">
         <v>6.2E-2</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>13</v>
+      <c r="K31" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1.1000000000000001</v>
@@ -5446,16 +6344,16 @@
       <c r="J32">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
+      <c r="K32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1.32</v>
@@ -5481,16 +6379,16 @@
       <c r="J33">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
+      <c r="K33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1.49</v>
@@ -5516,16 +6414,16 @@
       <c r="J34">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
+      <c r="K34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1.87</v>
@@ -5551,16 +6449,16 @@
       <c r="J35">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
+      <c r="K35" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>23</v>
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
       </c>
       <c r="C36">
         <v>2.46</v>
@@ -5586,51 +6484,51 @@
       <c r="J36">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
+      <c r="K36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="1">
         <v>5.13</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>0.30299999999999999</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>4.0599999999999996</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>0.17799999999999999</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="1">
         <v>10.32</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>0.42</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="1">
         <v>2.4</v>
       </c>
       <c r="J37">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
+      <c r="K37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1.63</v>
@@ -5656,16 +6554,16 @@
       <c r="J38">
         <v>0.12</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
+      <c r="K38" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
       </c>
       <c r="C39">
         <v>1.38</v>
@@ -5691,16 +6589,16 @@
       <c r="J39">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
+      <c r="K39" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
       <c r="C40">
         <v>1.32</v>
@@ -5726,16 +6624,16 @@
       <c r="J40">
         <v>0.115</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
+      <c r="K40" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1.1000000000000001</v>
@@ -5761,16 +6659,16 @@
       <c r="J41">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>13</v>
+      <c r="K41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
       </c>
       <c r="C42">
         <v>1.04</v>
@@ -5796,16 +6694,16 @@
       <c r="J42">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
+      <c r="K42" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1.51</v>
@@ -5831,16 +6729,16 @@
       <c r="J43">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>13</v>
+      <c r="K43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
       </c>
       <c r="C44">
         <v>1.1399999999999999</v>
@@ -5866,16 +6764,16 @@
       <c r="J44">
         <v>7.8E-2</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
+      <c r="K44" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1.06</v>
@@ -5901,16 +6799,16 @@
       <c r="J45">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>13</v>
+      <c r="K45" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>21</v>
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1.05</v>
@@ -5936,16 +6834,16 @@
       <c r="J46">
         <v>0.115</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>13</v>
+      <c r="K46" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1.19</v>
@@ -5971,16 +6869,16 @@
       <c r="J47">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
+      <c r="K47" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
       </c>
       <c r="C48">
         <v>3.03</v>
@@ -6006,43 +6904,43 @@
       <c r="J48">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
+      <c r="K48" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1">
         <v>7.96</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>0.219</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>9.48</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>0.21099999999999999</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="1">
         <v>8.2799999999999994</v>
       </c>
       <c r="H49">
         <v>0.13500000000000001</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="1">
         <v>6.94</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>0.24099999999999999</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
+      <c r="K49" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -6053,7 +6951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8F37F92-18B6-4C19-8D02-C0E818CB92AC}">
   <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6071,45 +6969,45 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2">
         <v>1.53</v>
@@ -6135,16 +7033,16 @@
       <c r="J2">
         <v>0.154</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
+      <c r="K2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3">
         <v>1.24</v>
@@ -6155,7 +7053,7 @@
       <c r="E3">
         <v>0.98</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>6.3E-2</v>
       </c>
       <c r="G3">
@@ -6170,16 +7068,16 @@
       <c r="J3">
         <v>0.129</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1.1000000000000001</v>
@@ -6205,16 +7103,16 @@
       <c r="J4">
         <v>0.10199999999999999</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
+      <c r="K4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1.07</v>
@@ -6240,16 +7138,16 @@
       <c r="J5">
         <v>0.114</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>13</v>
+      <c r="K5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
       </c>
       <c r="C6">
         <v>1.1000000000000001</v>
@@ -6275,16 +7173,16 @@
       <c r="J6">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
+      <c r="K6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1.23</v>
@@ -6310,21 +7208,21 @@
       <c r="J7">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
+      <c r="K7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
       </c>
       <c r="C8">
         <v>1.01</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
       <c r="E8">
@@ -6333,7 +7231,7 @@
       <c r="F8">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>2.29</v>
       </c>
       <c r="H8">
@@ -6345,24 +7243,24 @@
       <c r="J8">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>13</v>
+      <c r="K8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3">
         <v>0.98</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>0.84</v>
       </c>
       <c r="F9">
@@ -6374,22 +7272,22 @@
       <c r="H9">
         <v>0.13600000000000001</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <v>0.71</v>
       </c>
       <c r="J9">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>13</v>
+      <c r="K9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.1599999999999999</v>
@@ -6406,25 +7304,25 @@
       <c r="G10">
         <v>2.5099999999999998</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <v>0.123</v>
       </c>
       <c r="I10">
         <v>0.72</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>13</v>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
       </c>
       <c r="C11">
         <v>1.23</v>
@@ -6450,16 +7348,16 @@
       <c r="J11">
         <v>0.115</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12">
         <v>1.34</v>
@@ -6485,16 +7383,16 @@
       <c r="J12">
         <v>0.107</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>13</v>
+      <c r="K12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
       </c>
       <c r="C13">
         <v>1.96</v>
@@ -6520,16 +7418,16 @@
       <c r="J13">
         <v>0.16</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>13</v>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14">
         <v>1.33</v>
@@ -6555,16 +7453,16 @@
       <c r="J14">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>13</v>
+      <c r="K14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>1.21</v>
@@ -6590,16 +7488,16 @@
       <c r="J15">
         <v>0.13600000000000001</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>13</v>
+      <c r="K15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1.23</v>
@@ -6625,16 +7523,16 @@
       <c r="J16">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>13</v>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
       </c>
       <c r="C17">
         <v>1.1499999999999999</v>
@@ -6657,19 +7555,19 @@
       <c r="I17">
         <v>0.76</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="3">
         <v>4.2000000000000003E-2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>13</v>
+      <c r="K17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18">
         <v>1.18</v>
@@ -6695,16 +7593,16 @@
       <c r="J18">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>13</v>
+      <c r="K18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19">
         <v>1.26</v>
@@ -6715,7 +7613,7 @@
       <c r="E19">
         <v>0.9</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <v>8.4000000000000005E-2</v>
       </c>
       <c r="G19">
@@ -6730,51 +7628,51 @@
       <c r="J19">
         <v>0.11600000000000001</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>13</v>
+      <c r="K19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3">
         <v>0.98</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="3">
         <v>0.87</v>
       </c>
       <c r="F20">
         <v>8.8999999999999996E-2</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>1.91</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="3">
         <v>0.121</v>
       </c>
-      <c r="I20" s="4">
+      <c r="I20" s="3">
         <v>0.67</v>
       </c>
       <c r="J20">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>13</v>
+      <c r="K20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
       </c>
       <c r="C21">
         <v>1.17</v>
@@ -6800,16 +7698,16 @@
       <c r="J21">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>13</v>
+      <c r="K21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22">
         <v>1.26</v>
@@ -6835,16 +7733,16 @@
       <c r="J22">
         <v>6.8000000000000005E-2</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>13</v>
+      <c r="K22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23">
         <v>1.36</v>
@@ -6870,16 +7768,16 @@
       <c r="J23">
         <v>7.1999999999999995E-2</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>13</v>
+      <c r="K23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
       </c>
       <c r="C24">
         <v>2.09</v>
@@ -6905,16 +7803,16 @@
       <c r="J24">
         <v>0.252</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>13</v>
+      <c r="K24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
       </c>
       <c r="C25">
         <v>14.08</v>
@@ -6940,16 +7838,16 @@
       <c r="J25">
         <v>0.46100000000000002</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
+      <c r="K25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
       </c>
       <c r="C26">
         <v>3.01</v>
@@ -6975,16 +7873,16 @@
       <c r="J26">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
+      <c r="K26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
         <v>2.0499999999999998</v>
@@ -7010,16 +7908,16 @@
       <c r="J27">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
+      <c r="K27" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1.69</v>
@@ -7045,16 +7943,16 @@
       <c r="J28">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>13</v>
+      <c r="K28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>16</v>
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1.42</v>
@@ -7068,7 +7966,7 @@
       <c r="F29">
         <v>0.115</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="3">
         <v>2.84</v>
       </c>
       <c r="H29">
@@ -7080,16 +7978,16 @@
       <c r="J29">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
+      <c r="K29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1.31</v>
@@ -7109,22 +8007,22 @@
       <c r="H30">
         <v>0.2</v>
       </c>
-      <c r="I30" s="4">
+      <c r="I30" s="3">
         <v>0.47</v>
       </c>
       <c r="J30">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>13</v>
+      <c r="K30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1.55</v>
@@ -7150,27 +8048,27 @@
       <c r="J31">
         <v>6.2E-2</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>13</v>
+      <c r="K31" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="4">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>0.1</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>0.97</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="3">
         <v>0.08</v>
       </c>
       <c r="G32">
@@ -7185,16 +8083,16 @@
       <c r="J32">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
+      <c r="K32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1.32</v>
@@ -7208,10 +8106,10 @@
       <c r="F33">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G33" s="4">
+      <c r="G33" s="3">
         <v>2.84</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="3">
         <v>0.14199999999999999</v>
       </c>
       <c r="I33">
@@ -7220,16 +8118,16 @@
       <c r="J33">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
+      <c r="K33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1.49</v>
@@ -7252,19 +8150,19 @@
       <c r="I34">
         <v>0.47</v>
       </c>
-      <c r="J34" s="4">
+      <c r="J34" s="3">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
+      <c r="K34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1.87</v>
@@ -7290,16 +8188,16 @@
       <c r="J35">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
+      <c r="K35" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>23</v>
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
       </c>
       <c r="C36">
         <v>2.46</v>
@@ -7325,16 +8223,16 @@
       <c r="J36">
         <v>6.0999999999999999E-2</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
+      <c r="K36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>24</v>
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
       </c>
       <c r="C37">
         <v>5.13</v>
@@ -7360,16 +8258,16 @@
       <c r="J37">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
+      <c r="K37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1.63</v>
@@ -7395,16 +8293,16 @@
       <c r="J38">
         <v>0.12</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
+      <c r="K38" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
       </c>
       <c r="C39">
         <v>1.38</v>
@@ -7430,16 +8328,16 @@
       <c r="J39">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
+      <c r="K39" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
       <c r="C40">
         <v>1.32</v>
@@ -7465,16 +8363,16 @@
       <c r="J40">
         <v>0.115</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
+      <c r="K40" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1.1000000000000001</v>
@@ -7485,7 +8383,7 @@
       <c r="E41">
         <v>0.88</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="3">
         <v>7.0999999999999994E-2</v>
       </c>
       <c r="G41">
@@ -7500,21 +8398,21 @@
       <c r="J41">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>13</v>
+      <c r="K41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="4">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="3">
         <v>1.04</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D42" s="3">
         <v>0.09</v>
       </c>
       <c r="E42">
@@ -7535,16 +8433,16 @@
       <c r="J42">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
+      <c r="K42" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1.51</v>
@@ -7567,19 +8465,19 @@
       <c r="I43">
         <v>0.71</v>
       </c>
-      <c r="J43" s="4">
+      <c r="J43" s="3">
         <v>7.4999999999999997E-2</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>13</v>
+      <c r="K43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
       </c>
       <c r="C44">
         <v>1.1399999999999999</v>
@@ -7593,10 +8491,10 @@
       <c r="F44">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="3">
         <v>1.74</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44" s="3">
         <v>0.123</v>
       </c>
       <c r="I44">
@@ -7605,16 +8503,16 @@
       <c r="J44">
         <v>7.8E-2</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
+      <c r="K44" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1.06</v>
@@ -7634,22 +8532,22 @@
       <c r="H45">
         <v>0.13700000000000001</v>
       </c>
-      <c r="I45" s="4">
+      <c r="I45" s="3">
         <v>0.65</v>
       </c>
       <c r="J45">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>13</v>
+      <c r="K45" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>21</v>
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1.05</v>
@@ -7675,16 +8573,16 @@
       <c r="J46">
         <v>0.115</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>13</v>
+      <c r="K46" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1.19</v>
@@ -7692,7 +8590,7 @@
       <c r="D47">
         <v>0.121</v>
       </c>
-      <c r="E47" s="4">
+      <c r="E47" s="3">
         <v>0.83</v>
       </c>
       <c r="F47">
@@ -7710,16 +8608,16 @@
       <c r="J47">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
+      <c r="K47" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
       </c>
       <c r="C48">
         <v>3.03</v>
@@ -7745,16 +8643,16 @@
       <c r="J48">
         <v>7.9000000000000001E-2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
+      <c r="K48" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>24</v>
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
       </c>
       <c r="C49">
         <v>7.96</v>
@@ -7780,8 +8678,8 @@
       <c r="J49">
         <v>0.24099999999999999</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
+      <c r="K49" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -7792,7 +8690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55BBE6C-52C4-45A9-B6AB-7B57AFCF666F}">
   <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7810,45 +8708,45 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2">
         <v>2.91</v>
@@ -7874,16 +8772,16 @@
       <c r="J2">
         <v>5.8999999999999997E-2</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
+      <c r="K2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3">
         <v>2.0499999999999998</v>
@@ -7909,16 +8807,16 @@
       <c r="J3">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1.76</v>
@@ -7944,16 +8842,16 @@
       <c r="J4">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
+      <c r="K4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1.51</v>
@@ -7979,16 +8877,16 @@
       <c r="J5">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>13</v>
+      <c r="K5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
       </c>
       <c r="C6">
         <v>1.35</v>
@@ -7999,7 +8897,7 @@
       <c r="E6">
         <v>1.23</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>8.7999999999999995E-2</v>
       </c>
       <c r="G6">
@@ -8011,19 +8909,19 @@
       <c r="I6">
         <v>0.68</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>3.3000000000000002E-2</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
+      <c r="K6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1.47</v>
@@ -8049,30 +8947,30 @@
       <c r="J7">
         <v>0.06</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
+      <c r="K7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="4">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="3">
         <v>1.1200000000000001</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="3">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="3">
         <v>1.0900000000000001</v>
       </c>
       <c r="F8">
         <v>0.09</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>2.54</v>
       </c>
       <c r="H8">
@@ -8084,16 +8982,16 @@
       <c r="J8">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>13</v>
+      <c r="K8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
       </c>
       <c r="C9">
         <v>1.35</v>
@@ -8110,7 +9008,7 @@
       <c r="G9">
         <v>3</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>0.14399999999999999</v>
       </c>
       <c r="I9">
@@ -8119,16 +9017,16 @@
       <c r="J9">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>13</v>
+      <c r="K9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.58</v>
@@ -8148,22 +9046,22 @@
       <c r="H10">
         <v>0.17499999999999999</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="3">
         <v>0.63</v>
       </c>
       <c r="J10">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>13</v>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
       </c>
       <c r="C11">
         <v>1.83</v>
@@ -8180,7 +9078,7 @@
       <c r="G11">
         <v>4.37</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="1">
         <v>0.217</v>
       </c>
       <c r="I11">
@@ -8189,16 +9087,16 @@
       <c r="J11">
         <v>8.2000000000000003E-2</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12">
         <v>2.5299999999999998</v>
@@ -8212,10 +9110,10 @@
       <c r="F12">
         <v>0.127</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="1">
         <v>5.34</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="1">
         <v>0.25600000000000001</v>
       </c>
       <c r="I12">
@@ -8224,21 +9122,21 @@
       <c r="J12">
         <v>6.4000000000000001E-2</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>13</v>
+      <c r="K12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="2">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="1">
         <v>5.34</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>0.29199999999999998</v>
       </c>
       <c r="E13">
@@ -8247,28 +9145,28 @@
       <c r="F13">
         <v>0.187</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="1">
         <v>9.65</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>0.39900000000000002</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="1">
         <v>2.8</v>
       </c>
       <c r="J13">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>13</v>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14">
         <v>1.6</v>
@@ -8294,16 +9192,16 @@
       <c r="J14">
         <v>0.14899999999999999</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>13</v>
+      <c r="K14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>1.36</v>
@@ -8329,16 +9227,16 @@
       <c r="J15">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>13</v>
+      <c r="K15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1.25</v>
@@ -8364,16 +9262,16 @@
       <c r="J16">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>13</v>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
       </c>
       <c r="C17">
         <v>1.1599999999999999</v>
@@ -8384,7 +9282,7 @@
       <c r="E17">
         <v>0.88</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="3">
         <v>6.4000000000000001E-2</v>
       </c>
       <c r="G17">
@@ -8399,16 +9297,16 @@
       <c r="J17">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>13</v>
+      <c r="K17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18">
         <v>1.08</v>
@@ -8428,22 +9326,22 @@
       <c r="H18">
         <v>0.189</v>
       </c>
-      <c r="I18" s="4">
+      <c r="I18" s="3">
         <v>0.66</v>
       </c>
       <c r="J18">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>13</v>
+      <c r="K18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19">
         <v>1.67</v>
@@ -8469,21 +9367,21 @@
       <c r="J19">
         <v>0.09</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>13</v>
+      <c r="K19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="3">
         <v>0.92</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>9.4E-2</v>
       </c>
       <c r="E20">
@@ -8492,10 +9390,10 @@
       <c r="F20">
         <v>0.104</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>1.41</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="3">
         <v>0.107</v>
       </c>
       <c r="I20">
@@ -8504,16 +9402,16 @@
       <c r="J20">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>13</v>
+      <c r="K20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
       </c>
       <c r="C21">
         <v>1.06</v>
@@ -8521,7 +9419,7 @@
       <c r="D21">
         <v>0.104</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>0.84</v>
       </c>
       <c r="F21">
@@ -8539,16 +9437,16 @@
       <c r="J21">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>13</v>
+      <c r="K21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22">
         <v>1.1000000000000001</v>
@@ -8571,19 +9469,19 @@
       <c r="I22">
         <v>0.68</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="3">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>13</v>
+      <c r="K22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23">
         <v>1.24</v>
@@ -8606,19 +9504,19 @@
       <c r="I23">
         <v>0.69</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="3">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>13</v>
+      <c r="K23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
       </c>
       <c r="C24">
         <v>3.38</v>
@@ -8626,69 +9524,69 @@
       <c r="D24">
         <v>0.154</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="1">
         <v>5.4</v>
       </c>
       <c r="F24">
         <v>0.23300000000000001</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="1">
         <v>7.1</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="1">
         <v>0.253</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="1">
         <v>5.01</v>
       </c>
       <c r="J24">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>13</v>
+      <c r="K24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C25" s="2">
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
+      </c>
+      <c r="C25" s="1">
         <v>8.02</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="1">
         <v>0.216</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="1">
         <v>9.48</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="1">
         <v>0.214</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="1">
         <v>8.24</v>
       </c>
       <c r="H25">
         <v>0.13900000000000001</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="1">
         <v>7.06</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="1">
         <v>0.251</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
+      <c r="K25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
       </c>
       <c r="C26">
         <v>3.03</v>
@@ -8714,16 +9612,16 @@
       <c r="J26">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
+      <c r="K26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
         <v>2.0099999999999998</v>
@@ -8749,16 +9647,16 @@
       <c r="J27">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
+      <c r="K27" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1.56</v>
@@ -8784,16 +9682,16 @@
       <c r="J28">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>13</v>
+      <c r="K28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>16</v>
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1.4</v>
@@ -8819,16 +9717,16 @@
       <c r="J29">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
+      <c r="K29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1.24</v>
@@ -8854,16 +9752,16 @@
       <c r="J30">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>13</v>
+      <c r="K30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1.33</v>
@@ -8889,16 +9787,16 @@
       <c r="J31">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>13</v>
+      <c r="K31" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
       </c>
       <c r="C32">
         <v>1.1000000000000001</v>
@@ -8924,16 +9822,16 @@
       <c r="J32">
         <v>5.5E-2</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
+      <c r="K32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1.32</v>
@@ -8959,16 +9857,16 @@
       <c r="J33">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
+      <c r="K33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1.48</v>
@@ -8994,16 +9892,16 @@
       <c r="J34">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
+      <c r="K34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1.8</v>
@@ -9029,16 +9927,16 @@
       <c r="J35">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
+      <c r="K35" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>23</v>
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
       </c>
       <c r="C36">
         <v>2.54</v>
@@ -9064,51 +9962,51 @@
       <c r="J36">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
+      <c r="K36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="2">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C37" s="1">
         <v>5.14</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="1">
         <v>0.29799999999999999</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="1">
         <v>4.01</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="1">
         <v>0.17699999999999999</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="1">
         <v>10.01</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="1">
         <v>0.40300000000000002</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="1">
         <v>2.63</v>
       </c>
       <c r="J37">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
+      <c r="K37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1.61</v>
@@ -9134,16 +10032,16 @@
       <c r="J38">
         <v>0.14899999999999999</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
+      <c r="K38" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
       </c>
       <c r="C39">
         <v>1.37</v>
@@ -9169,16 +10067,16 @@
       <c r="J39">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
+      <c r="K39" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
       <c r="C40">
         <v>1.25</v>
@@ -9204,16 +10102,16 @@
       <c r="J40">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
+      <c r="K40" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1.1299999999999999</v>
@@ -9239,16 +10137,16 @@
       <c r="J41">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>13</v>
+      <c r="K41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
       </c>
       <c r="C42">
         <v>1.0900000000000001</v>
@@ -9274,16 +10172,16 @@
       <c r="J42">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
+      <c r="K42" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1.68</v>
@@ -9309,16 +10207,16 @@
       <c r="J43">
         <v>0.09</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>13</v>
+      <c r="K43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
       </c>
       <c r="C44">
         <v>0.88</v>
@@ -9344,16 +10242,16 @@
       <c r="J44">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
+      <c r="K44" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1.01</v>
@@ -9379,16 +10277,16 @@
       <c r="J45">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>13</v>
+      <c r="K45" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>21</v>
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1.08</v>
@@ -9414,16 +10312,16 @@
       <c r="J46">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>13</v>
+      <c r="K46" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1.24</v>
@@ -9440,7 +10338,7 @@
       <c r="G47">
         <v>3.91</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="1">
         <v>0.20699999999999999</v>
       </c>
       <c r="I47">
@@ -9449,16 +10347,16 @@
       <c r="J47">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
+      <c r="K47" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
       </c>
       <c r="C48">
         <v>3.34</v>
@@ -9469,13 +10367,13 @@
       <c r="E48">
         <v>5.39</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="1">
         <v>0.23100000000000001</v>
       </c>
       <c r="G48">
         <v>7.32</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="1">
         <v>0.25700000000000001</v>
       </c>
       <c r="I48">
@@ -9484,43 +10382,43 @@
       <c r="J48">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
+      <c r="K48" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="2">
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="1">
         <v>7.98</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="1">
         <v>0.214</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="1">
         <v>9.4499999999999993</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="1">
         <v>0.217</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="1">
         <v>8.26</v>
       </c>
       <c r="H49">
         <v>0.13600000000000001</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="1">
         <v>6.97</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="1">
         <v>0.251</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
+      <c r="K49" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -9531,7 +10429,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2276E11D-AA1C-47EB-90DD-FAB7954E87E1}">
   <dimension ref="A1:K49"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9549,45 +10447,45 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" t="s">
+        <v>46</v>
       </c>
       <c r="C2">
         <v>1.62</v>
@@ -9613,16 +10511,16 @@
       <c r="J2">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
+      <c r="K2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>14</v>
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3">
         <v>1.1200000000000001</v>
@@ -9648,16 +10546,16 @@
       <c r="J3">
         <v>8.7999999999999995E-2</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>13</v>
+      <c r="K3" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4">
         <v>1.1100000000000001</v>
@@ -9683,16 +10581,16 @@
       <c r="J4">
         <v>0.14199999999999999</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>13</v>
+      <c r="K4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
+      <c r="A5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
       </c>
       <c r="C5">
         <v>1.06</v>
@@ -9712,22 +10610,22 @@
       <c r="H5">
         <v>0.155</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>0.55000000000000004</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>13</v>
+      <c r="K5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
+      <c r="A6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" t="s">
+        <v>51</v>
       </c>
       <c r="C6">
         <v>1.1200000000000001</v>
@@ -9753,16 +10651,16 @@
       <c r="J6">
         <v>8.5999999999999993E-2</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>13</v>
+      <c r="K6" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>18</v>
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
       </c>
       <c r="C7">
         <v>1.0900000000000001</v>
@@ -9788,16 +10686,16 @@
       <c r="J7">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="K7" s="1" t="s">
-        <v>13</v>
+      <c r="K7" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>53</v>
       </c>
       <c r="C8">
         <v>1.01</v>
@@ -9811,7 +10709,7 @@
       <c r="F8">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>2.14</v>
       </c>
       <c r="H8">
@@ -9823,24 +10721,24 @@
       <c r="J8">
         <v>7.5999999999999998E-2</v>
       </c>
-      <c r="K8" s="1" t="s">
-        <v>13</v>
+      <c r="K8" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C9" s="4">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="3">
         <v>0.95</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="3">
         <v>7.8E-2</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="3">
         <v>0.81</v>
       </c>
       <c r="F9">
@@ -9849,7 +10747,7 @@
       <c r="G9">
         <v>2.33</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>0.123</v>
       </c>
       <c r="I9">
@@ -9858,16 +10756,16 @@
       <c r="J9">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K9" s="1" t="s">
-        <v>13</v>
+      <c r="K9" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>21</v>
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1.1000000000000001</v>
@@ -9893,16 +10791,16 @@
       <c r="J10">
         <v>8.6999999999999994E-2</v>
       </c>
-      <c r="K10" s="1" t="s">
-        <v>13</v>
+      <c r="K10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:11">
-      <c r="A11" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>22</v>
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>56</v>
       </c>
       <c r="C11">
         <v>1.1499999999999999</v>
@@ -9913,7 +10811,7 @@
       <c r="E11">
         <v>0.97</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>6.3E-2</v>
       </c>
       <c r="G11">
@@ -9928,16 +10826,16 @@
       <c r="J11">
         <v>0.08</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>13</v>
+      <c r="K11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
+      <c r="A12" t="s">
+        <v>45</v>
+      </c>
+      <c r="B12" t="s">
+        <v>57</v>
       </c>
       <c r="C12">
         <v>1.37</v>
@@ -9963,16 +10861,16 @@
       <c r="J12">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>13</v>
+      <c r="K12" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>24</v>
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
       </c>
       <c r="C13">
         <v>1.92</v>
@@ -9998,16 +10896,16 @@
       <c r="J13">
         <v>0.14399999999999999</v>
       </c>
-      <c r="K13" s="1" t="s">
-        <v>13</v>
+      <c r="K13" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>12</v>
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
       </c>
       <c r="C14">
         <v>1.34</v>
@@ -10033,16 +10931,16 @@
       <c r="J14">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>13</v>
+      <c r="K14" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15">
         <v>1.3</v>
@@ -10068,16 +10966,16 @@
       <c r="J15">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="K15" s="1" t="s">
-        <v>13</v>
+      <c r="K15" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" t="s">
+        <v>49</v>
       </c>
       <c r="C16">
         <v>1.24</v>
@@ -10097,22 +10995,22 @@
       <c r="H16">
         <v>0.22700000000000001</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="3">
         <v>0.78</v>
       </c>
       <c r="J16">
         <v>5.0999999999999997E-2</v>
       </c>
-      <c r="K16" s="1" t="s">
-        <v>13</v>
+      <c r="K16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s">
+        <v>50</v>
       </c>
       <c r="C17">
         <v>1.1299999999999999</v>
@@ -10138,16 +11036,16 @@
       <c r="J17">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="K17" s="1" t="s">
-        <v>13</v>
+      <c r="K17" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18">
         <v>1.1299999999999999</v>
@@ -10173,16 +11071,16 @@
       <c r="J18">
         <v>0.06</v>
       </c>
-      <c r="K18" s="1" t="s">
-        <v>13</v>
+      <c r="K18" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:11">
-      <c r="A19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
       </c>
       <c r="C19">
         <v>1.22</v>
@@ -10208,33 +11106,33 @@
       <c r="J19">
         <v>0.112</v>
       </c>
-      <c r="K19" s="1" t="s">
-        <v>13</v>
+      <c r="K19" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
       </c>
       <c r="C20">
         <v>1.03</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="3">
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="3">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="G20" s="4">
+      <c r="G20" s="3">
         <v>2.09</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="3">
         <v>0.124</v>
       </c>
       <c r="I20">
@@ -10243,24 +11141,24 @@
       <c r="J20">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="K20" s="1" t="s">
-        <v>13</v>
+      <c r="K20" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:11">
-      <c r="A21" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C21" s="4">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="3">
         <v>1.02</v>
       </c>
       <c r="D21">
         <v>0.09</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="3">
         <v>0.92</v>
       </c>
       <c r="F21">
@@ -10278,16 +11176,16 @@
       <c r="J21">
         <v>0.13300000000000001</v>
       </c>
-      <c r="K21" s="1" t="s">
-        <v>13</v>
+      <c r="K21" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22">
         <v>1.24</v>
@@ -10310,19 +11208,19 @@
       <c r="I22">
         <v>0.98</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="3">
         <v>0.05</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>13</v>
+      <c r="K22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="s">
+        <v>56</v>
       </c>
       <c r="C23">
         <v>1.37</v>
@@ -10348,16 +11246,16 @@
       <c r="J23">
         <v>6.2E-2</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>13</v>
+      <c r="K23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>57</v>
       </c>
       <c r="C24">
         <v>2.6</v>
@@ -10383,16 +11281,16 @@
       <c r="J24">
         <v>0.24</v>
       </c>
-      <c r="K24" s="1" t="s">
-        <v>13</v>
+      <c r="K24" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" t="s">
+        <v>58</v>
       </c>
       <c r="C25">
         <v>14.02</v>
@@ -10418,16 +11316,16 @@
       <c r="J25">
         <v>0.47199999999999998</v>
       </c>
-      <c r="K25" s="1" t="s">
-        <v>13</v>
+      <c r="K25" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>12</v>
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" t="s">
+        <v>46</v>
       </c>
       <c r="C26">
         <v>3.03</v>
@@ -10453,16 +11351,16 @@
       <c r="J26">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>13</v>
+      <c r="K26" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
       </c>
       <c r="C27">
         <v>2.0099999999999998</v>
@@ -10488,16 +11386,16 @@
       <c r="J27">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="K27" s="1" t="s">
-        <v>13</v>
+      <c r="K27" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>15</v>
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
       </c>
       <c r="C28">
         <v>1.56</v>
@@ -10523,16 +11421,16 @@
       <c r="J28">
         <v>5.1999999999999998E-2</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>13</v>
+      <c r="K28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>16</v>
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
       </c>
       <c r="C29">
         <v>1.4</v>
@@ -10546,7 +11444,7 @@
       <c r="F29">
         <v>0.1</v>
       </c>
-      <c r="G29" s="4">
+      <c r="G29" s="3">
         <v>2.56</v>
       </c>
       <c r="H29">
@@ -10558,16 +11456,16 @@
       <c r="J29">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>13</v>
+      <c r="K29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>17</v>
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" t="s">
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1.24</v>
@@ -10578,7 +11476,7 @@
       <c r="E30">
         <v>1.1299999999999999</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="3">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G30">
@@ -10593,16 +11491,16 @@
       <c r="J30">
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="K30" s="1" t="s">
-        <v>13</v>
+      <c r="K30" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>18</v>
+      <c r="A31" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" t="s">
+        <v>52</v>
       </c>
       <c r="C31">
         <v>1.33</v>
@@ -10625,27 +11523,27 @@
       <c r="I31">
         <v>0.67</v>
       </c>
-      <c r="J31" s="4">
+      <c r="J31" s="3">
         <v>3.7999999999999999E-2</v>
       </c>
-      <c r="K31" s="1" t="s">
-        <v>13</v>
+      <c r="K31" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32" s="4">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D32" s="4">
+      <c r="D32" s="3">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="E32" s="4">
+      <c r="E32" s="3">
         <v>1.07</v>
       </c>
       <c r="F32">
@@ -10657,22 +11555,22 @@
       <c r="H32">
         <v>0.192</v>
       </c>
-      <c r="I32" s="4">
+      <c r="I32" s="3">
         <v>0.56000000000000005</v>
       </c>
       <c r="J32">
         <v>5.5E-2</v>
       </c>
-      <c r="K32" s="1" t="s">
-        <v>13</v>
+      <c r="K32" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:11">
-      <c r="A33" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>20</v>
+      <c r="A33" t="s">
+        <v>60</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
       </c>
       <c r="C33">
         <v>1.32</v>
@@ -10683,13 +11581,13 @@
       <c r="E33">
         <v>1.1599999999999999</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="3">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="G33">
         <v>2.95</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="3">
         <v>0.158</v>
       </c>
       <c r="I33">
@@ -10698,16 +11596,16 @@
       <c r="J33">
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="K33" s="1" t="s">
-        <v>13</v>
+      <c r="K33" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:11">
-      <c r="A34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>21</v>
+      <c r="A34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1.48</v>
@@ -10733,16 +11631,16 @@
       <c r="J34">
         <v>4.8000000000000001E-2</v>
       </c>
-      <c r="K34" s="1" t="s">
-        <v>13</v>
+      <c r="K34" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>22</v>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1.8</v>
@@ -10768,16 +11666,16 @@
       <c r="J35">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K35" s="1" t="s">
-        <v>13</v>
+      <c r="K35" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>23</v>
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
       </c>
       <c r="C36">
         <v>2.54</v>
@@ -10803,16 +11701,16 @@
       <c r="J36">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="K36" s="1" t="s">
-        <v>13</v>
+      <c r="K36" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>24</v>
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>58</v>
       </c>
       <c r="C37">
         <v>5.14</v>
@@ -10838,16 +11736,16 @@
       <c r="J37">
         <v>9.9000000000000005E-2</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>13</v>
+      <c r="K37" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>12</v>
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" t="s">
+        <v>46</v>
       </c>
       <c r="C38">
         <v>1.61</v>
@@ -10873,16 +11771,16 @@
       <c r="J38">
         <v>0.14899999999999999</v>
       </c>
-      <c r="K38" s="1" t="s">
-        <v>13</v>
+      <c r="K38" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>14</v>
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" t="s">
+        <v>48</v>
       </c>
       <c r="C39">
         <v>1.37</v>
@@ -10908,16 +11806,16 @@
       <c r="J39">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K39" s="1" t="s">
-        <v>13</v>
+      <c r="K39" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>15</v>
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
       </c>
       <c r="C40">
         <v>1.25</v>
@@ -10943,16 +11841,16 @@
       <c r="J40">
         <v>7.6999999999999999E-2</v>
       </c>
-      <c r="K40" s="1" t="s">
-        <v>13</v>
+      <c r="K40" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>16</v>
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" t="s">
+        <v>50</v>
       </c>
       <c r="C41">
         <v>1.1299999999999999</v>
@@ -10963,7 +11861,7 @@
       <c r="E41">
         <v>0.91</v>
       </c>
-      <c r="F41" s="4">
+      <c r="F41" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="G41">
@@ -10978,16 +11876,16 @@
       <c r="J41">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="K41" s="1" t="s">
-        <v>13</v>
+      <c r="K41" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>17</v>
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" t="s">
+        <v>51</v>
       </c>
       <c r="C42">
         <v>1.0900000000000001</v>
@@ -11007,22 +11905,22 @@
       <c r="H42">
         <v>0.187</v>
       </c>
-      <c r="I42" s="4">
+      <c r="I42" s="3">
         <v>0.66</v>
       </c>
       <c r="J42">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K42" s="1" t="s">
-        <v>13</v>
+      <c r="K42" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>18</v>
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" t="s">
+        <v>52</v>
       </c>
       <c r="C43">
         <v>1.68</v>
@@ -11048,21 +11946,21 @@
       <c r="J43">
         <v>0.09</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>13</v>
+      <c r="K43" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C44" s="4">
+      <c r="A44" t="s">
+        <v>61</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="3">
         <v>0.88</v>
       </c>
-      <c r="D44" s="4">
+      <c r="D44" s="3">
         <v>8.2000000000000003E-2</v>
       </c>
       <c r="E44">
@@ -11071,10 +11969,10 @@
       <c r="F44">
         <v>0.106</v>
       </c>
-      <c r="G44" s="4">
+      <c r="G44" s="3">
         <v>1.37</v>
       </c>
-      <c r="H44" s="4">
+      <c r="H44" s="3">
         <v>0.106</v>
       </c>
       <c r="I44">
@@ -11083,16 +11981,16 @@
       <c r="J44">
         <v>7.2999999999999995E-2</v>
       </c>
-      <c r="K44" s="1" t="s">
-        <v>13</v>
+      <c r="K44" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
+      <c r="A45" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" t="s">
+        <v>54</v>
       </c>
       <c r="C45">
         <v>1.01</v>
@@ -11118,16 +12016,16 @@
       <c r="J45">
         <v>8.4000000000000005E-2</v>
       </c>
-      <c r="K45" s="1" t="s">
-        <v>13</v>
+      <c r="K45" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>21</v>
+      <c r="A46" t="s">
+        <v>61</v>
+      </c>
+      <c r="B46" t="s">
+        <v>55</v>
       </c>
       <c r="C46">
         <v>1.08</v>
@@ -11135,7 +12033,7 @@
       <c r="D46">
         <v>0.109</v>
       </c>
-      <c r="E46" s="4">
+      <c r="E46" s="3">
         <v>0.82</v>
       </c>
       <c r="F46">
@@ -11153,16 +12051,16 @@
       <c r="J46">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K46" s="1" t="s">
-        <v>13</v>
+      <c r="K46" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>22</v>
+      <c r="A47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B47" t="s">
+        <v>56</v>
       </c>
       <c r="C47">
         <v>1.24</v>
@@ -11185,19 +12083,19 @@
       <c r="I47">
         <v>0.69</v>
       </c>
-      <c r="J47" s="4">
+      <c r="J47" s="3">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="K47" s="1" t="s">
-        <v>13</v>
+      <c r="K47" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>23</v>
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" t="s">
+        <v>57</v>
       </c>
       <c r="C48">
         <v>3.34</v>
@@ -11223,16 +12121,16 @@
       <c r="J48">
         <v>8.1000000000000003E-2</v>
       </c>
-      <c r="K48" s="1" t="s">
-        <v>13</v>
+      <c r="K48" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>24</v>
+      <c r="A49" t="s">
+        <v>61</v>
+      </c>
+      <c r="B49" t="s">
+        <v>58</v>
       </c>
       <c r="C49">
         <v>7.98</v>
@@ -11258,8 +12156,8 @@
       <c r="J49">
         <v>0.251</v>
       </c>
-      <c r="K49" s="1" t="s">
-        <v>13</v>
+      <c r="K49" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
